--- a/dist/modele_alimentation_pilotageh.xlsx
+++ b/dist/modele_alimentation_pilotageh.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\EMECI\COURS\M2PID 2\Lean Management\Dashboard\PilotageH_autonome\PilotageH_autonome\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E213E0A-B1D0-4267-B1DF-6A1DBCECF844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{611CD23A-CF50-453C-B2CB-21ED46A60F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -91,13 +91,13 @@
     <t>Montage Elec</t>
   </si>
   <si>
-    <t>BPRS3G</t>
-  </si>
-  <si>
-    <t>BTUR</t>
-  </si>
-  <si>
-    <t>TT1</t>
+    <t>BANC 1</t>
+  </si>
+  <si>
+    <t>BANC 2</t>
+  </si>
+  <si>
+    <t>BANC 3</t>
   </si>
 </sst>
 </file>
@@ -512,7 +512,7 @@
       </c>
       <c r="F2" s="3">
         <f ca="1">RANDBETWEEN(DATE(2026,1,1),DATE(2026,12,31))</f>
-        <v>46361</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -533,7 +533,7 @@
       </c>
       <c r="F3" s="3">
         <f ca="1">RANDBETWEEN(DATE(2026,1,1),DATE(2026,12,31))</f>
-        <v>46177</v>
+        <v>46138</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -545,19 +545,19 @@
       </c>
       <c r="C4" s="1">
         <f ca="1">RANDBETWEEN(100,2500)</f>
-        <v>1536</v>
+        <v>1826</v>
       </c>
       <c r="D4" s="1">
         <f ca="1">RANDBETWEEN(100,E4)</f>
-        <v>2445</v>
+        <v>816</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="D4:E19" ca="1" si="0">RANDBETWEEN(100,2500)</f>
-        <v>2494</v>
+        <v>2481</v>
       </c>
       <c r="F4" s="3">
         <f t="shared" ref="F4:F52" ca="1" si="1">RANDBETWEEN(DATE(2026,1,1),DATE(2026,12,31))</f>
-        <v>46178</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -569,19 +569,19 @@
       </c>
       <c r="C5" s="1">
         <f t="shared" ref="C5:C52" ca="1" si="2">RANDBETWEEN(100,2500)</f>
-        <v>885</v>
+        <v>837</v>
       </c>
       <c r="D5" s="1">
         <f t="shared" ref="D5:D52" ca="1" si="3">RANDBETWEEN(100,E5)</f>
-        <v>514</v>
+        <v>372</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>673</v>
+        <v>492</v>
       </c>
       <c r="F5" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46029</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -593,19 +593,19 @@
       </c>
       <c r="C6" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1017</v>
+        <v>2149</v>
       </c>
       <c r="D6" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>609</v>
+        <v>563</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2332</v>
+        <v>1719</v>
       </c>
       <c r="F6" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46312</v>
+        <v>46215</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -617,19 +617,19 @@
       </c>
       <c r="C7" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2075</v>
+        <v>597</v>
       </c>
       <c r="D7" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>1164</v>
+        <v>240</v>
       </c>
       <c r="E7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1596</v>
+        <v>433</v>
       </c>
       <c r="F7" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46227</v>
+        <v>46264</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -641,19 +641,19 @@
       </c>
       <c r="C8" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>383</v>
+        <v>1162</v>
       </c>
       <c r="D8" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="E8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1057</v>
+        <v>345</v>
       </c>
       <c r="F8" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46250</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -665,19 +665,19 @@
       </c>
       <c r="C9" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1585</v>
+        <v>1889</v>
       </c>
       <c r="D9" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>1761</v>
+        <v>363</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1931</v>
+        <v>2320</v>
       </c>
       <c r="F9" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46072</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -689,19 +689,19 @@
       </c>
       <c r="C10" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2350</v>
+        <v>226</v>
       </c>
       <c r="D10" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>734</v>
+        <v>896</v>
       </c>
       <c r="E10" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1142</v>
+        <v>2439</v>
       </c>
       <c r="F10" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46056</v>
+        <v>46032</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -713,19 +713,19 @@
       </c>
       <c r="C11" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>846</v>
+        <v>352</v>
       </c>
       <c r="D11" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>134</v>
+        <v>629</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>220</v>
+        <v>755</v>
       </c>
       <c r="F11" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46144</v>
+        <v>46051</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -737,19 +737,19 @@
       </c>
       <c r="C12" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1041</v>
+        <v>900</v>
       </c>
       <c r="D12" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>445</v>
+        <v>726</v>
       </c>
       <c r="E12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>686</v>
+        <v>970</v>
       </c>
       <c r="F12" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46372</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -761,19 +761,19 @@
       </c>
       <c r="C13" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>791</v>
+        <v>1636</v>
       </c>
       <c r="D13" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>1293</v>
+        <v>225</v>
       </c>
       <c r="E13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1883</v>
+        <v>1881</v>
       </c>
       <c r="F13" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46114</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -785,19 +785,19 @@
       </c>
       <c r="C14" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>239</v>
+        <v>1341</v>
       </c>
       <c r="D14" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>639</v>
+        <v>823</v>
       </c>
       <c r="E14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>770</v>
+        <v>841</v>
       </c>
       <c r="F14" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46298</v>
+        <v>46323</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -809,19 +809,19 @@
       </c>
       <c r="C15" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2310</v>
+        <v>1250</v>
       </c>
       <c r="D15" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>858</v>
+        <v>119</v>
       </c>
       <c r="E15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1287</v>
+        <v>1758</v>
       </c>
       <c r="F15" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46386</v>
+        <v>46378</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -833,19 +833,19 @@
       </c>
       <c r="C16" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1978</v>
+        <v>323</v>
       </c>
       <c r="D16" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>207</v>
+        <v>121</v>
       </c>
       <c r="E16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>617</v>
+        <v>321</v>
       </c>
       <c r="F16" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46160</v>
+        <v>46200</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -857,19 +857,19 @@
       </c>
       <c r="C17" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2460</v>
+        <v>985</v>
       </c>
       <c r="D17" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>1357</v>
+        <v>1367</v>
       </c>
       <c r="E17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2352</v>
+        <v>2000</v>
       </c>
       <c r="F17" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46187</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -881,19 +881,19 @@
       </c>
       <c r="C18" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>188</v>
+        <v>1994</v>
       </c>
       <c r="D18" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>1614</v>
+        <v>215</v>
       </c>
       <c r="E18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1699</v>
+        <v>323</v>
       </c>
       <c r="F18" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46190</v>
+        <v>46151</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -905,19 +905,19 @@
       </c>
       <c r="C19" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>228</v>
+        <v>497</v>
       </c>
       <c r="D19" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>1739</v>
+        <v>1796</v>
       </c>
       <c r="E19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1789</v>
+        <v>2118</v>
       </c>
       <c r="F19" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46325</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -929,19 +929,19 @@
       </c>
       <c r="C20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>478</v>
+        <v>1527</v>
       </c>
       <c r="D20" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>131</v>
+        <v>535</v>
       </c>
       <c r="E20" s="1">
         <f t="shared" ref="E20:E52" ca="1" si="4">RANDBETWEEN(100,2500)</f>
-        <v>1215</v>
+        <v>818</v>
       </c>
       <c r="F20" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46344</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -953,19 +953,19 @@
       </c>
       <c r="C21" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1881</v>
+        <v>365</v>
       </c>
       <c r="D21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>266</v>
+        <v>171</v>
       </c>
       <c r="E21" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1057</v>
+        <v>921</v>
       </c>
       <c r="F21" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46362</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -977,19 +977,19 @@
       </c>
       <c r="C22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1630</v>
+        <v>724</v>
       </c>
       <c r="D22" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>959</v>
+        <v>1081</v>
       </c>
       <c r="E22" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1550</v>
+        <v>1219</v>
       </c>
       <c r="F22" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46061</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -1001,19 +1001,19 @@
       </c>
       <c r="C23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1489</v>
+        <v>332</v>
       </c>
       <c r="D23" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>814</v>
+        <v>1026</v>
       </c>
       <c r="E23" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>2256</v>
+        <v>1542</v>
       </c>
       <c r="F23" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46077</v>
+        <v>46139</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -1025,19 +1025,19 @@
       </c>
       <c r="C24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>612</v>
+        <v>1322</v>
       </c>
       <c r="D24" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>890</v>
+        <v>585</v>
       </c>
       <c r="E24" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>976</v>
+        <v>2266</v>
       </c>
       <c r="F24" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46216</v>
+        <v>46221</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -1049,19 +1049,19 @@
       </c>
       <c r="C25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>315</v>
+        <v>1842</v>
       </c>
       <c r="D25" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>550</v>
+        <v>468</v>
       </c>
       <c r="E25" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>672</v>
+        <v>1656</v>
       </c>
       <c r="F25" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46106</v>
+        <v>46370</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -1073,19 +1073,19 @@
       </c>
       <c r="C26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1237</v>
+        <v>2266</v>
       </c>
       <c r="D26" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>110</v>
+        <v>356</v>
       </c>
       <c r="E26" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>613</v>
+        <v>1996</v>
       </c>
       <c r="F26" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46151</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -1097,19 +1097,19 @@
       </c>
       <c r="C27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1255</v>
+        <v>2208</v>
       </c>
       <c r="D27" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>956</v>
+        <v>130</v>
       </c>
       <c r="E27" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1564</v>
+        <v>133</v>
       </c>
       <c r="F27" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46038</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -1121,19 +1121,19 @@
       </c>
       <c r="C28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="D28" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>528</v>
+        <v>1304</v>
       </c>
       <c r="E28" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1169</v>
+        <v>1472</v>
       </c>
       <c r="F28" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46138</v>
+        <v>46372</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -1145,19 +1145,19 @@
       </c>
       <c r="C29" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1865</v>
+        <v>450</v>
       </c>
       <c r="D29" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>1903</v>
+        <v>1627</v>
       </c>
       <c r="E29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1957</v>
+        <v>2324</v>
       </c>
       <c r="F29" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46191</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -1169,19 +1169,19 @@
       </c>
       <c r="C30" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1008</v>
+        <v>692</v>
       </c>
       <c r="D30" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>663</v>
+        <v>593</v>
       </c>
       <c r="E30" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1281</v>
+        <v>802</v>
       </c>
       <c r="F30" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46369</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -1193,19 +1193,19 @@
       </c>
       <c r="C31" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1876</v>
+        <v>1421</v>
       </c>
       <c r="D31" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>935</v>
+        <v>1436</v>
       </c>
       <c r="E31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1007</v>
+        <v>1837</v>
       </c>
       <c r="F31" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46263</v>
+        <v>46151</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -1217,19 +1217,19 @@
       </c>
       <c r="C32" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>470</v>
+        <v>1261</v>
       </c>
       <c r="D32" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>168</v>
+        <v>197</v>
       </c>
       <c r="E32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>573</v>
+        <v>637</v>
       </c>
       <c r="F32" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46318</v>
+        <v>46172</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -1241,19 +1241,19 @@
       </c>
       <c r="C33" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>483</v>
+        <v>406</v>
       </c>
       <c r="D33" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>316</v>
+        <v>540</v>
       </c>
       <c r="E33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1806</v>
+        <v>973</v>
       </c>
       <c r="F33" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46077</v>
+        <v>46144</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -1265,19 +1265,19 @@
       </c>
       <c r="C34" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>999</v>
+        <v>1826</v>
       </c>
       <c r="D34" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>111</v>
+        <v>884</v>
       </c>
       <c r="E34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>868</v>
+        <v>1043</v>
       </c>
       <c r="F34" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46332</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -1289,19 +1289,19 @@
       </c>
       <c r="C35" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>346</v>
+        <v>2017</v>
       </c>
       <c r="D35" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>1204</v>
+        <v>170</v>
       </c>
       <c r="E35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1604</v>
+        <v>1848</v>
       </c>
       <c r="F35" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46346</v>
+        <v>46312</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -1313,19 +1313,19 @@
       </c>
       <c r="C36" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>311</v>
+        <v>1001</v>
       </c>
       <c r="D36" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>1319</v>
+        <v>1555</v>
       </c>
       <c r="E36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1430</v>
+        <v>1757</v>
       </c>
       <c r="F36" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46328</v>
+        <v>46063</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -1337,19 +1337,19 @@
       </c>
       <c r="C37" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1688</v>
+        <v>1347</v>
       </c>
       <c r="D37" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>115</v>
+        <v>913</v>
       </c>
       <c r="E37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>131</v>
+        <v>970</v>
       </c>
       <c r="F37" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46057</v>
+        <v>46175</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -1361,19 +1361,19 @@
       </c>
       <c r="C38" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1088</v>
+        <v>862</v>
       </c>
       <c r="D38" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>398</v>
+        <v>167</v>
       </c>
       <c r="E38" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1392</v>
+        <v>1232</v>
       </c>
       <c r="F38" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46381</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -1385,19 +1385,19 @@
       </c>
       <c r="C39" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2216</v>
+        <v>2179</v>
       </c>
       <c r="D39" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>1624</v>
+        <v>770</v>
       </c>
       <c r="E39" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1903</v>
+        <v>1926</v>
       </c>
       <c r="F39" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46320</v>
+        <v>46037</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -1409,19 +1409,19 @@
       </c>
       <c r="C40" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2221</v>
+        <v>1756</v>
       </c>
       <c r="D40" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>254</v>
+        <v>1074</v>
       </c>
       <c r="E40" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>585</v>
+        <v>2278</v>
       </c>
       <c r="F40" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46202</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -1433,19 +1433,19 @@
       </c>
       <c r="C41" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1855</v>
+        <v>1646</v>
       </c>
       <c r="D41" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>465</v>
+        <v>506</v>
       </c>
       <c r="E41" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1318</v>
+        <v>2179</v>
       </c>
       <c r="F41" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46137</v>
+        <v>46334</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -1457,19 +1457,19 @@
       </c>
       <c r="C42" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1100</v>
+        <v>1618</v>
       </c>
       <c r="D42" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E42" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>392</v>
+        <v>475</v>
       </c>
       <c r="F42" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46209</v>
+        <v>46361</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -1481,19 +1481,19 @@
       </c>
       <c r="C43" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1476</v>
+        <v>2155</v>
       </c>
       <c r="D43" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>1335</v>
+        <v>453</v>
       </c>
       <c r="E43" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1776</v>
+        <v>654</v>
       </c>
       <c r="F43" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46324</v>
+        <v>46361</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -1505,19 +1505,19 @@
       </c>
       <c r="C44" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2370</v>
+        <v>2314</v>
       </c>
       <c r="D44" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>1566</v>
+        <v>1444</v>
       </c>
       <c r="E44" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>2074</v>
+        <v>2474</v>
       </c>
       <c r="F44" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46379</v>
+        <v>46371</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -1529,19 +1529,19 @@
       </c>
       <c r="C45" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2308</v>
+        <v>2103</v>
       </c>
       <c r="D45" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>236</v>
+        <v>113</v>
       </c>
       <c r="E45" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>340</v>
+        <v>1659</v>
       </c>
       <c r="F45" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46212</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -1553,19 +1553,19 @@
       </c>
       <c r="C46" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>564</v>
+        <v>656</v>
       </c>
       <c r="D46" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>977</v>
+        <v>1613</v>
       </c>
       <c r="E46" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1924</v>
+        <v>2283</v>
       </c>
       <c r="F46" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46023</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -1577,19 +1577,19 @@
       </c>
       <c r="C47" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>248</v>
+        <v>2436</v>
       </c>
       <c r="D47" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>139</v>
+        <v>1580</v>
       </c>
       <c r="E47" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1290</v>
+        <v>2428</v>
       </c>
       <c r="F47" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46270</v>
+        <v>46089</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -1601,19 +1601,19 @@
       </c>
       <c r="C48" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2327</v>
+        <v>540</v>
       </c>
       <c r="D48" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E48" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>595</v>
+        <v>1563</v>
       </c>
       <c r="F48" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46296</v>
+        <v>46360</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -1625,19 +1625,19 @@
       </c>
       <c r="C49" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2291</v>
+        <v>310</v>
       </c>
       <c r="D49" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>114</v>
+        <v>260</v>
       </c>
       <c r="E49" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>689</v>
+        <v>780</v>
       </c>
       <c r="F49" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46097</v>
+        <v>46362</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="C50" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>273</v>
+        <v>1785</v>
       </c>
       <c r="D50" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>1443</v>
+        <v>509</v>
       </c>
       <c r="E50" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>2171</v>
+        <v>1332</v>
       </c>
       <c r="F50" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46108</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -1673,19 +1673,19 @@
       </c>
       <c r="C51" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2025</v>
+        <v>1178</v>
       </c>
       <c r="D51" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>143</v>
+        <v>619</v>
       </c>
       <c r="E51" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>158</v>
+        <v>1500</v>
       </c>
       <c r="F51" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46337</v>
+        <v>46196</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
@@ -1697,19 +1697,19 @@
       </c>
       <c r="C52" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2406</v>
+        <v>2167</v>
       </c>
       <c r="D52" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>131</v>
+        <v>306</v>
       </c>
       <c r="E52" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>306</v>
+        <v>1455</v>
       </c>
       <c r="F52" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46262</v>
+        <v>46143</v>
       </c>
     </row>
   </sheetData>
